--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DE0785-174D-4180-960D-591814A545B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B99621-68D5-48EA-A39A-0CCD53B40315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>nombrerazonsocial</t>
   </si>
@@ -50,9 +50,6 @@
     <t>correo</t>
   </si>
   <si>
-    <t>formadepago</t>
-  </si>
-  <si>
     <t>contacto</t>
   </si>
   <si>
@@ -83,10 +80,25 @@
     <t>SHEILA</t>
   </si>
   <si>
-    <t>TRASFERENCIA</t>
-  </si>
-  <si>
-    <t>PUE</t>
+    <t>PUE(PAGO EN UNA SOLA EXHIBICION)</t>
+  </si>
+  <si>
+    <t>tiempoentrega</t>
+  </si>
+  <si>
+    <t>De 3 a 5 días</t>
+  </si>
+  <si>
+    <t>pago</t>
+  </si>
+  <si>
+    <t>CONTADO</t>
+  </si>
+  <si>
+    <t>formapago</t>
+  </si>
+  <si>
+    <t>Transferencia Electronica Fondos</t>
   </si>
 </sst>
 </file>
@@ -469,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -480,11 +492,12 @@
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -499,45 +512,57 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
       <c r="D2">
         <v>5543647896</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B99621-68D5-48EA-A39A-0CCD53B40315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5138D754-9E59-4850-BD4B-9551CA94B37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
@@ -80,9 +80,6 @@
     <t>SHEILA</t>
   </si>
   <si>
-    <t>PUE(PAGO EN UNA SOLA EXHIBICION)</t>
-  </si>
-  <si>
     <t>tiempoentrega</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>Transferencia Electronica Fondos</t>
+  </si>
+  <si>
+    <t>PUE (Pago en una sola exhibición)</t>
   </si>
 </sst>
 </file>
@@ -493,6 +493,8 @@
     <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -518,16 +520,16 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -553,16 +555,16 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5138D754-9E59-4850-BD4B-9551CA94B37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7F9B31-674D-422D-AF7F-3579EB7A68BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>bimb26</t>
   </si>
   <si>
-    <t>BIMBO SA DE CV</t>
-  </si>
-  <si>
     <t>BMB230326XXRRFS</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>PUE (Pago en una sola exhibición)</t>
+  </si>
+  <si>
+    <t>BIMBO S.A. DE C.V.</t>
   </si>
 </sst>
 </file>
@@ -514,22 +514,22 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -537,34 +537,34 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
       <c r="D2">
         <v>5543647896</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7F9B31-674D-422D-AF7F-3579EB7A68BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC8BB20-1EEC-453E-8051-5DD4FD36AB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>nombrerazonsocial</t>
   </si>
@@ -53,9 +53,6 @@
     <t>contacto</t>
   </si>
   <si>
-    <t>metodopago</t>
-  </si>
-  <si>
     <t>idproveedor</t>
   </si>
   <si>
@@ -75,27 +72,6 @@
   </si>
   <si>
     <t>SHEILA</t>
-  </si>
-  <si>
-    <t>tiempoentrega</t>
-  </si>
-  <si>
-    <t>De 3 a 5 días</t>
-  </si>
-  <si>
-    <t>pago</t>
-  </si>
-  <si>
-    <t>CONTADO</t>
-  </si>
-  <si>
-    <t>formapago</t>
-  </si>
-  <si>
-    <t>Transferencia Electronica Fondos</t>
-  </si>
-  <si>
-    <t>PUE (Pago en una sola exhibición)</t>
   </si>
   <si>
     <t>BIMBO S.A. DE C.V.</t>
@@ -481,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -491,15 +467,11 @@
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -514,57 +486,33 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2">
         <v>5543647896</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>nombrerazonsocial</t>
   </si>
@@ -75,12 +75,34 @@
   </si>
   <si>
     <t>BIMBO S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>ID_PROVEEDOR</t>
+  </si>
+  <si>
+    <t>NOMBRE_RAZON_SOCIAL</t>
+  </si>
+  <si>
+    <t>PAGO</t>
+  </si>
+  <si>
+    <t>METODO_PAGO</t>
+  </si>
+  <si>
+    <t>TIEMPO_ENTREGA</t>
+  </si>
+  <si>
+    <t>FORMA_PAGO</t>
+  </si>
+  <si>
+    <t>ACTIVO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -457,24 +479,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.36328125" collapsed="false"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="16.36328125" collapsed="false"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="16.7265625" collapsed="false"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625" collapsed="false"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="16.0" collapsed="false"/>
+    <col min="6" max="6" customWidth="true" width="34.0" collapsed="false"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="8.08984375" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -490,6 +512,21 @@
       </c>
       <c r="G1" t="s">
         <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC8BB20-1EEC-453E-8051-5DD4FD36AB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4A4D54-6925-43FD-8B8A-232E51310998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
+    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>nombrerazonsocial</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>RFC</t>
   </si>
@@ -53,9 +50,6 @@
     <t>contacto</t>
   </si>
   <si>
-    <t>idproveedor</t>
-  </si>
-  <si>
     <t>bimb26</t>
   </si>
   <si>
@@ -81,18 +75,6 @@
   </si>
   <si>
     <t>NOMBRE_RAZON_SOCIAL</t>
-  </si>
-  <si>
-    <t>PAGO</t>
-  </si>
-  <si>
-    <t>METODO_PAGO</t>
-  </si>
-  <si>
-    <t>TIEMPO_ENTREGA</t>
-  </si>
-  <si>
-    <t>FORMA_PAGO</t>
   </si>
   <si>
     <t>ACTIVO</t>
@@ -102,7 +84,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -479,77 +460,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="10.36328125" collapsed="false"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="16.36328125" collapsed="false"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="16.7265625" collapsed="false"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625" collapsed="false"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="16.0" collapsed="false"/>
-    <col min="6" max="6" customWidth="true" width="34.0" collapsed="false"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="8.08984375" collapsed="false"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>5543647896</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4A4D54-6925-43FD-8B8A-232E51310998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD7DBC2-3A1C-4F13-A5CF-A9269B532C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>RFC</t>
   </si>
@@ -78,6 +78,186 @@
   </si>
   <si>
     <t>ACTIVO</t>
+  </si>
+  <si>
+    <t>lact01</t>
+  </si>
+  <si>
+    <t>LACTEOS DEL VALLE S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>LDV240115AB1</t>
+  </si>
+  <si>
+    <t>lacteos.valle@gmail.com</t>
+  </si>
+  <si>
+    <t>Calle Norte 45 No. 120, Col. Industrial Vallejo, Azcapotzalco, Ciudad de México</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>sabri02</t>
+  </si>
+  <si>
+    <t>SABRITAS S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>SAB850101XYZ</t>
+  </si>
+  <si>
+    <t>sabritas.contacto@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Río Consulado No. 300, Col. Ampliación Del Gas, Azcapotzalco, Ciudad de México</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>coca03</t>
+  </si>
+  <si>
+    <t>COCA COLA FEMSA S.A.B. DE C.V.</t>
+  </si>
+  <si>
+    <t>CCF920101AAA</t>
+  </si>
+  <si>
+    <t>cocacola.femsa@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Insurgentes Sur No. 1602, Col. Crédito Constructor, Benito Juárez, Ciudad de México</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>nest04</t>
+  </si>
+  <si>
+    <t>NESTLE MEXICO S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>NME830101BBB</t>
+  </si>
+  <si>
+    <t>nestle.mex@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Ejército Nacional No. 843, Col. Granada, Miguel Hidalgo, Ciudad de México</t>
+  </si>
+  <si>
+    <t>LAURA</t>
+  </si>
+  <si>
+    <t>herd05</t>
+  </si>
+  <si>
+    <t>HERDEZ S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>HER920202CCC</t>
+  </si>
+  <si>
+    <t>herdez.contacto@gmail.com</t>
+  </si>
+  <si>
+    <t>Calle Monte Pelvoux No. 215, Col. Lomas de Chapultepec, Miguel Hidalgo, Ciudad de México</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>jume06</t>
+  </si>
+  <si>
+    <t>JUMEX S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>JUM880303DDD</t>
+  </si>
+  <si>
+    <t>jumex@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Central No. 100, Col. Nueva Industrial Vallejo, Gustavo A. Madero, Ciudad de México</t>
+  </si>
+  <si>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>bacha07</t>
+  </si>
+  <si>
+    <t>BACHOCO S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>BAC910404EEE</t>
+  </si>
+  <si>
+    <t>bachoco@gmail.com</t>
+  </si>
+  <si>
+    <t>Calle 5 No. 89, Col. Agrícola Oriental, Iztacalco, Ciudad de México</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>lala08</t>
+  </si>
+  <si>
+    <t>GRUPO LALA S.A.B. DE C.V.</t>
+  </si>
+  <si>
+    <t>LAL920505FFF</t>
+  </si>
+  <si>
+    <t>lala@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Paseo de la Reforma No. 222, Col. Juárez, Cuauhtémoc, Ciudad de México</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>mode09</t>
+  </si>
+  <si>
+    <t>MODELO S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>MOD930606GGG</t>
+  </si>
+  <si>
+    <t>modelo@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Lago Alberto No. 156, Col. Anáhuac, Miguel Hidalgo, Ciudad de México</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>peps10</t>
+  </si>
+  <si>
+    <t>PEPSICO MEXICO S.A. DE C.V.</t>
+  </si>
+  <si>
+    <t>PEP940707HHH</t>
+  </si>
+  <si>
+    <t>pepsico@gmail.com</t>
+  </si>
+  <si>
+    <t>Av. Santa Fe No. 485, Col. Cruz Manca, Cuajimalpa, Ciudad de México</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
   </si>
 </sst>
 </file>
@@ -460,16 +640,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="86.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -519,6 +700,269 @@
       </c>
       <c r="G2" t="s">
         <v>9</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>5512345678</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>5523456789</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5">
+        <v>5534567890</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>5545678901</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>5556789012</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>5567890123</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>5578901234</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>5589012345</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11">
+        <v>5590123456</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12">
+        <v>5511122233</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PROVEEDORES.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD7DBC2-3A1C-4F13-A5CF-A9269B532C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591514D5-92A4-4950-928E-91B40A3ACFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EBE529F0-1989-4E0B-B87D-8E5A162CA571}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>RFC</t>
   </si>
@@ -258,12 +258,64 @@
   </si>
   <si>
     <t>ANDREA</t>
+  </si>
+  <si>
+    <t>avsu15</t>
+  </si>
+  <si>
+    <t>AVANTE SUPPLIES</t>
+  </si>
+  <si>
+    <t>ASU150413FE4</t>
+  </si>
+  <si>
+    <t>ventas6@avantesps.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cjon. Vocnete Beristain #151 Int. 2 Col. Aplicación Asturias Cuauhtemoc </t>
+  </si>
+  <si>
+    <t>Elsa Leticia Flores</t>
+  </si>
+  <si>
+    <t>PAGO</t>
+  </si>
+  <si>
+    <t>METODO_PAGO</t>
+  </si>
+  <si>
+    <t>TIEMPO_ENTREGA</t>
+  </si>
+  <si>
+    <t>FORMA_PAGO</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>5543647896</t>
+  </si>
+  <si>
+    <t>Daniela</t>
+  </si>
+  <si>
+    <t>PUE(PAGO EN UNA SOLA EXHIBICION)</t>
+  </si>
+  <si>
+    <t>De 3 a 5 dias</t>
+  </si>
+  <si>
+    <t>Transferencia Electronica Fondos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -640,20 +692,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CBE3-6A92-456E-9134-BFBEA6F1CED4}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="86.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="28.6328125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="16.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="25.453125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="86.36328125" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.90625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="7.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -676,10 +728,22 @@
         <v>3</v>
       </c>
       <c r="H1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -689,8 +753,8 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>5543647896</v>
+      <c r="D2" t="s">
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -699,13 +763,25 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -731,7 +807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -757,7 +833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -783,7 +859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -809,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -835,7 +911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -861,7 +937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -887,7 +963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -913,7 +989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -939,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -962,14 +1038,41 @@
         <v>73</v>
       </c>
       <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13">
+        <v>5555555555</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{9E8DA580-04F7-4207-BBF7-CACE85CDF085}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{BEBA4C49-389C-4DDF-BA14-30964A46AE44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>